--- a/data/por_departamento/Usulután/establecimientos_salud.xlsx
+++ b/data/por_departamento/Usulután/establecimientos_salud.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benjamin.escalante\Desktop\Unidades de Salud\gis-unidades-salud\data\por_departamento\Usulután\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE90601-8C4A-4267-A19A-4E14FB06278F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318B80DD-ACB6-4C9F-AF8E-22685139BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
